--- a/results/log_pv_inst_fit/log_pv_inst_fit_densities_fdensity_estimates.xlsx
+++ b/results/log_pv_inst_fit/log_pv_inst_fit_densities_fdensity_estimates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,41 +462,11 @@
           <t>densities-ML_ErrorFE-queen-Running ML_ErrorFE:queen for log_pv_inst_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-inverse_distance-Running PooledOLS:inverse_distance for log_pv_inst_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-k_nearest-Running PooledOLS:k_nearest for log_pv_inst_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>densities-PooledOLS-queen-Running PooledOLS:queen for log_pv_inst_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-inverse_distance-Running PanelRE:inverse_distance for log_pv_inst_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-k_nearest-Running PanelRE:k_nearest for log_pv_inst_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>densities-PanelRE-queen-Running PanelRE:queen for log_pv_inst_fit ~ (densities): fdensity + ['log_income', 'log_hholds', 'log_sunny_hours']</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fdensity</t>
+          <t>D(Firms)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,43 +512,13 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>0.006***</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>-0.061***</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-0.061***</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>-0.061***</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>-0.000</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -624,43 +564,13 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>0.240***</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-0.823***</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-0.823***</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-0.823***</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1.951***</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>1.951***</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>1.951***</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -706,43 +616,13 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>0.003*</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.016+</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.016+</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.016+</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -788,126 +668,96 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>0.188***</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.381*</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.381*</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.381*</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>-0.169***</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>-0.169***</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.169***</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W_fdensity</t>
+          <t>Spatial term, ρ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.010</t>
+          <t>0.880***</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.008*</t>
+          <t>0.706***</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.009**</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>0.596***</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.962***</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.785***</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.691***</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W_log_income</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.573***</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.742***</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.946***</t>
-        </is>
-      </c>
+          <t>Spatial term, λ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.973***</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.890***</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.839***</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W_log_hholds</t>
+          <t>W(D(Firms))</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.065***</t>
+          <t>-0.010</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.010*</t>
+          <t>-0.008*</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.008***</t>
+          <t>-0.009**</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -916,32 +766,26 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W_log_sunny_hours</t>
+          <t>W(Income)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.286***</t>
+          <t>0.573***</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.331***</t>
+          <t>0.742***</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.322***</t>
+          <t>0.946***</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -950,891 +794,320 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W_log_pv_inst_fit</t>
+          <t>W(Households)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.880***</t>
+          <t>-0.065***</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.706***</t>
+          <t>-0.010*</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.596***</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.962***</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.785***</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0.691***</t>
-        </is>
-      </c>
+          <t>-0.008***</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>W(Sunny hours)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.850</t>
+          <t>-0.286***</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.828</t>
+          <t>-0.331***</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.812</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.849</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.824</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.804</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.000</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.295</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.396</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.169</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.169</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.169</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.111</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.111</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.111</t>
-        </is>
-      </c>
+          <t>-0.322***</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aic</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>-9801.403</t>
+          <t>0.850</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-9383.781</t>
+          <t>0.828</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-9175.104</t>
+          <t>0.812</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-9770.599</t>
+          <t>0.849</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-9283.797</t>
+          <t>0.824</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9016.058</t>
+          <t>0.804</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9784.836</t>
+          <t>0.000</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-9196.562</t>
+          <t>0.295</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8826.855</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1351.403</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1351.403</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1351.403</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2769.826</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2769.826</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2769.826</t>
+          <t>0.396</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>schwarz</t>
+          <t>AIC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>-9750.659</t>
+          <t>-9801.403</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-9333.037</t>
+          <t>-9383.781</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-9124.360</t>
+          <t>-9175.104</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-9742.408</t>
+          <t>-9770.599</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-9255.606</t>
+          <t>-9283.797</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8987.867</t>
+          <t>-9016.058</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-9762.283</t>
+          <t>-9784.836</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-9174.009</t>
+          <t>-9196.562</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-8804.302</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>1379.594</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1379.594</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>1379.594</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2798.017</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2798.017</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2798.017</t>
+          <t>-8826.855</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>llr</t>
+          <t>BIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4909.701</t>
+          <t>-9750.659</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4700.890</t>
+          <t>-9333.037</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4596.552</t>
+          <t>-9124.360</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4890.299</t>
+          <t>-9742.408</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>4646.898</t>
+          <t>-9255.606</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4513.029</t>
+          <t>-8987.867</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4896.418</t>
+          <t>-9762.283</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4602.281</t>
+          <t>-9174.009</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4417.427</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>-670.702</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-670.702</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>-670.702</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-1379.913</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-1379.913</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>-1379.913</t>
+          <t>-8804.302</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>n_obs</t>
+          <t>Log-Likelihood</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4909.701</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4700.890</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4596.552</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4890.299</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4646.898</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4513.029</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4896.418</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>4602.281</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2076</t>
+          <t>4417.427</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tests</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    66.933308   1      0.0
-1  LM Marginal Spatial (LM2)    17.875854   1      0.0
-2             LM Joint (LMJ)  4799.613910   2      0.0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df  p-value
-0       LM Marginal RE (LM1)    66.933308   1      0.0
-1  LM Marginal Spatial (LM2)     8.767059   1      0.0
-2             LM Joint (LMJ)  4556.929062   2      0.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        Test    Statistic  df       p-value
-0       LM Marginal RE (LM1)    66.933308   1  0.000000e+00
-1  LM Marginal Spatial (LM2)     7.908556   1  1.332268e-15
-2             LM Joint (LMJ)  4542.613005   2  0.000000e+00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial  155.815486  1     0.0
-1  Hausman Specification Test -159.445374  4     1.0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial   38.902927  1     0.0
-1  Hausman Specification Test -159.445374  4     1.0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                         Test   Statistic df p-value
-0      LM Conditional Spatial    26.11717  1     0.0
-1  Hausman Specification Test -159.445374  4     1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>outputs</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           fdensity      0.00418  0.001419   2.946686  0.003212
-1         log_income     -0.06581  0.073559  -0.894667  0.370965
-2         log_hholds     0.000867  0.001196   0.724513  0.468751
-3    log_sunny_hours     0.165586   0.03449    4.80099  0.000002
-4         W_fdensity    -0.009683  0.027371   -0.35375  0.723526
-5       W_log_income     0.573034  0.173334   3.305946  0.000947
-6       W_log_hholds    -0.065254  0.018746  -3.481012    0.0005
-7  W_log_sunny_hours    -0.286441  0.054502  -5.255604       0.0
-8  W_log_pv_inst_fit     0.880413   0.02852  30.870176       0.0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           fdensity     0.003788  0.001535   2.468652  0.013562
-1         log_income     0.004263  0.075085   0.056769  0.954729
-2         log_hholds     0.001311  0.001288   1.017983  0.308686
-3    log_sunny_hours     0.151579  0.035032   4.326838  0.000015
-4         W_fdensity    -0.008394  0.004247  -1.976589  0.048088
-5       W_log_income     0.742031  0.094179   7.878959       0.0
-6       W_log_hholds    -0.009563  0.003823  -2.501088  0.012381
-7  W_log_sunny_hours    -0.331298  0.046061  -7.192632       0.0
-8  W_log_pv_inst_fit     0.706305  0.020903  33.790467       0.0</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           fdensity     0.003353    0.0016    2.09568  0.036111
-1         log_income     0.042883  0.075264   0.569764  0.568838
-2         log_hholds     0.001526   0.00134   1.139138  0.254646
-3    log_sunny_hours     0.114414  0.035776   3.198103  0.001383
-4         W_fdensity    -0.009299   0.00336  -2.767838  0.005643
-5       W_log_income     0.945654  0.087124  10.854129       0.0
-6       W_log_hholds    -0.008366  0.002187  -3.825152  0.000131
-7  W_log_sunny_hours    -0.321739  0.044501    -7.2299       0.0
-8  W_log_pv_inst_fit     0.596187  0.021349  27.925745       0.0</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err   zt_stat      prob
-0           fdensity     0.003825   0.00142  2.694474   0.00705
-1         log_income     0.017019  0.026644  0.638753  0.522984
-2         log_hholds     0.001085  0.001194  0.908919  0.363393
-3    log_sunny_hours     0.068178  0.025305  2.694248  0.007055
-4  W_log_pv_inst_fit     0.961576   0.00988    97.329       0.0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           fdensity     0.003773  0.001535   2.458207  0.013963
-1         log_income     0.394776  0.037697   10.47231       0.0
-2         log_hholds     0.001671  0.001291    1.29432  0.195555
-3    log_sunny_hours     0.022619  0.025336   0.892777  0.371977
-4  W_log_pv_inst_fit     0.784557  0.015857  49.476664       0.0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           var_names coefficients   std_err    zt_stat      prob
-0           fdensity     0.003929   0.00162   2.425619  0.015282
-1         log_income     0.589801  0.041639  14.164498       0.0
-2         log_hholds     0.001778  0.001362   1.305838  0.191608
-3    log_sunny_hours     0.002109  0.026659   0.079115  0.936941
-4  W_log_pv_inst_fit     0.691429  0.017237  40.113929       0.0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err     zt_stat      prob
-0         fdensity     0.004025  0.001417    2.839481  0.004519
-1       log_income    -0.048817  0.073162   -0.667249  0.504613
-2       log_hholds     0.001272  0.001188     1.07033  0.284471
-3  log_sunny_hours     0.165327   0.03451    4.790729  0.000002
-4           lambda     0.972534  0.007663  126.908012       0.0</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         fdensity     0.004871  0.001488   3.274078   0.00106
-1       log_income     0.150148  0.071902   2.088225  0.036778
-2       log_hholds     0.002532  0.001223   2.069711  0.038479
-3  log_sunny_hours      0.19123  0.035255   5.424256       0.0
-4           lambda     0.890225  0.010095  88.188308       0.0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         fdensity     0.005514  0.001576   3.499111  0.000467
-1       log_income     0.239782  0.071677   3.345332  0.000822
-2       log_hholds     0.003084  0.001206   2.557684  0.010537
-3  log_sunny_hours     0.188253  0.036485   5.159746       0.0
-4           lambda     0.838725  0.012409  67.587738       0.0</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     5.412458  0.529376  10.224212       0.0
-1         fdensity    -0.060779   0.00516 -11.778068       0.0
-2       log_income    -0.823429  0.084295  -9.768442       0.0
-3       log_hholds     0.016309  0.008921   1.828111  0.067677
-4  log_sunny_hours     0.380706  0.160258   2.375576  0.017612</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     5.412458  0.529376  10.224212       0.0
-1         fdensity    -0.060779   0.00516 -11.778068       0.0
-2       log_income    -0.823429  0.084295  -9.768442       0.0
-3       log_hholds     0.016309  0.008921   1.828111  0.067677
-4  log_sunny_hours     0.380706  0.160258   2.375576  0.017612</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT     5.412458  0.529376  10.224212       0.0
-1         fdensity    -0.060779   0.00516 -11.778068       0.0
-2       log_income    -0.823429  0.084295  -9.768442       0.0
-3       log_hholds     0.016309  0.008921   1.828111  0.067677
-4  log_sunny_hours     0.380706  0.160258   2.375576  0.017612</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.675279  0.211213 -22.135353       0.0
-1         fdensity    -0.000189  0.002616  -0.072388  0.942293
-2       log_income     1.951203    0.0447  43.650625       0.0
-3       log_hholds     0.000272  0.002234   0.121905  0.902974
-4  log_sunny_hours    -0.168917  0.043668  -3.868207   0.00011</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.675279  0.211213 -22.135353       0.0
-1         fdensity    -0.000189  0.002616  -0.072388  0.942293
-2       log_income     1.951203    0.0447  43.650625       0.0
-3       log_hholds     0.000272  0.002234   0.121905  0.902974
-4  log_sunny_hours    -0.168917  0.043668  -3.868207   0.00011</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         var_names coefficients   std_err    zt_stat      prob
-0         CONSTANT    -4.675279  0.211213 -22.135353       0.0
-1         fdensity    -0.000189  0.002616  -0.072388  0.942293
-2       log_income     1.951203    0.0447  43.650625       0.0
-3       log_hholds     0.000272  0.002234   0.121905  0.902974
-4  log_sunny_hours    -0.168917  0.043668  -3.868207   0.00011</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>effects</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_inverse_distance  \
-fdensity                                    -0.046012   
-log_income                                   4.241451   
-log_hholds                                  -0.538408   
-log_sunny_hours                             -1.010606   
-                 direct_ML_LagFE(SLX)_inverse_distance  \
-fdensity                                      0.004180   
-log_income                                   -0.065810   
-log_hholds                                    0.000867   
-log_sunny_hours                               0.165586   
-                 indirect_ML_LagFE(SLX)_inverse_distance  
-fdensity                                       -0.050192  
-log_income                                      4.307261  
-log_hholds                                     -0.539275  
-log_sunny_hours                                -1.176192  </t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_k_nearest  \
-fdensity                             -0.015683   
-log_income                            2.541051   
-log_hholds                           -0.028095   
-log_sunny_hours                      -0.611924   
-                 direct_ML_LagFE(SLX)_k_nearest  \
-fdensity                               0.003788   
-log_income                             0.004263   
-log_hholds                             0.001311   
-log_sunny_hours                        0.151579   
-                 indirect_ML_LagFE(SLX)_k_nearest  
-fdensity                                -0.019471  
-log_income                               2.536789  
-log_hholds                              -0.029406  
-log_sunny_hours                         -0.763503  </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE(SLX)_queen  direct_ML_LagFE(SLX)_queen  \
-fdensity                         -0.014724                    0.003353   
-log_income                        2.448005                    0.042883   
-log_hholds                       -0.016939                    0.001526   
-log_sunny_hours                  -0.513419                    0.114414   
-                 indirect_ML_LagFE(SLX)_queen  
-fdensity                            -0.018077  
-log_income                           2.405123  
-log_hholds                          -0.018465  
-log_sunny_hours                     -0.627833  </t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_inverse_distance  \
-fdensity                                0.099543   
-log_income                              0.442929   
-log_hholds                              0.028249   
-log_sunny_hours                         1.774354   
-                 direct_ML_LagFE_inverse_distance  \
-fdensity                                 0.003825   
-log_income                               0.017019   
-log_hholds                               0.001085   
-log_sunny_hours                          0.068178   
-                 indirect_ML_LagFE_inverse_distance  
-fdensity                                   0.095718  
-log_income                                 0.425910  
-log_hholds                                 0.027164  
-log_sunny_hours                            1.706176  </t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_k_nearest  direct_ML_LagFE_k_nearest  \
-fdensity                         0.017514                   0.003773   
-log_income                       1.832393                   0.394776   
-log_hholds                       0.007755                   0.001671   
-log_sunny_hours                  0.104990                   0.022619   
-                 indirect_ML_LagFE_k_nearest  
-fdensity                            0.013741  
-log_income                          1.437618  
-log_hholds                          0.006084  
-log_sunny_hours                     0.082371  </t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 total_ML_LagFE_queen  direct_ML_LagFE_queen  \
-fdensity                     0.012732               0.003929   
-log_income                   1.911397               0.589801   
-log_hholds                   0.005762               0.001778   
-log_sunny_hours              0.006835               0.002109   
-                 indirect_ML_LagFE_queen  
-fdensity                        0.008804  
-log_income                      1.321595  
-log_hholds                      0.003984  
-log_sunny_hours                 0.004726  </t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>lambda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.973***</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.890***</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>0.839***</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CONSTANT</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>5.412***</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>5.412***</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>5.412***</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>-4.675***</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>-4.675***</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>-4.675***</t>
+          <t>N obs.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2076</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2076</t>
         </is>
       </c>
     </row>
